--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>136553688</v>
       </c>
       <c r="B12" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>136553688</v>
       </c>
       <c r="B12" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136553521</v>
       </c>
       <c r="B4" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136553688</v>
       </c>
       <c r="B12" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>136553688</v>
       </c>
       <c r="B12" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136553521</v>
       </c>
       <c r="B4" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136553688</v>
       </c>
       <c r="B12" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136553521</v>
       </c>
       <c r="B4" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136553688</v>
       </c>
       <c r="B12" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136553521</v>
       </c>
       <c r="B4" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136553688</v>
       </c>
       <c r="B12" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>136553688</v>
       </c>
       <c r="B12" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136553521</v>
       </c>
       <c r="B4" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136553688</v>
       </c>
       <c r="B12" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
